--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2640,8 +2640,8 @@
       <c r="P19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" s="9" t="n">
-        <v>1</v>
+      <c r="Q19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="P101" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -14269,7 +14269,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2264,7 +2268,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5455,7 +5463,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5762,7 +5774,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6275,7 +6291,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6893,7 +6913,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7200,7 +7224,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -8020,7 +8048,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8222,7 +8254,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8630,7 +8666,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9668,7 +9708,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9874,7 +9918,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -9975,7 +10023,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10379,7 +10431,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10581,7 +10637,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10888,7 +10948,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10989,7 +11053,11 @@
       <c r="AB100" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC100" s="4" t="inlineStr"/>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11090,7 +11158,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11191,7 +11263,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11292,7 +11368,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11700,7 +11780,11 @@
       <c r="AB107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11902,7 +11986,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12920,7 +13008,11 @@
       <c r="AB119" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -13328,7 +13420,11 @@
       <c r="AB123" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC123" s="4" t="inlineStr"/>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 29 clubs short</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>1</v>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>1</v>
@@ -10610,8 +10610,8 @@
       <c r="S96" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T96" s="9" t="n">
-        <v>0</v>
+      <c r="T96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
@@ -11123,7 +11123,7 @@
         <v>5</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11329,20 +11329,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+      <c r="P103" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q103" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R103" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S103" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13704,8 +13704,8 @@
       <c r="S126" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
@@ -14926,7 +14926,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14959,13 +14959,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -15124,7 +15124,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="10" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1843,8 +1843,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3810,8 +3810,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5248,8 +5248,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6803,8 +6803,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -7369,13 +7369,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8144,8 +8144,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="P79" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q79" s="10" t="n">
         <v>2</v>
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>4</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10822,11 +10822,11 @@
       <c r="U98" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>3</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>7</v>
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10883,13 +10883,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>1</v>
@@ -10927,8 +10927,8 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>3</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11303,13 +11303,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11347,11 +11347,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>7</v>
@@ -11499,7 +11499,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11569,8 +11569,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -12154,7 +12154,7 @@
         </is>
       </c>
       <c r="P111" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         <v>2</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>1</v>
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13823,8 +13823,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -14002,7 +14002,7 @@
         <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" s="9" t="n">
         <v>1</v>
@@ -14299,7 +14299,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14530,7 +14530,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14662,7 +14662,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14761,7 +14761,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14926,13 +14926,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -14959,7 +14959,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -14992,7 +14992,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15157,7 +15157,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC130"/>
+  <dimension ref="A1:AC132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -967,17 +967,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="7" t="n">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1173,17 +1173,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1214,8 +1214,8 @@
       <c r="T5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U5" s="9" t="n">
-        <v>0</v>
+      <c r="U5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>2</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1480,17 +1480,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1892,17 +1892,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2098,17 +2098,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2203,17 +2203,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2308,17 +2308,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="7" t="n">
@@ -2413,17 +2413,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2865,8 +2865,8 @@
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="9" t="n">
-        <v>3</v>
+      <c r="V21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2922,13 +2922,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3443,17 +3443,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3653,13 +3653,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3754,17 +3754,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="7" t="n">
@@ -3855,17 +3855,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4305,11 +4305,11 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W35" s="9" t="n">
-        <v>0</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W35" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>4</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4465,17 +4465,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
@@ -4512,8 +4512,8 @@
       <c r="V37" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W37" s="9" t="n">
-        <v>3</v>
+      <c r="W37" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>4</v>
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4776,17 +4776,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="7" t="n">
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4859,11 +4859,11 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>7803937</v>
+        <v>28681060</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Changeway Bilingual Suzhou Toastmasters Club</t>
+          <t>6:30 Toastmasters Club</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -4881,17 +4881,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
@@ -4919,8 +4919,8 @@
       <c r="S41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="10" t="n">
-        <v>1</v>
+      <c r="T41" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U41" s="9" t="n">
         <v>0</v>
@@ -4931,26 +4931,20 @@
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X41" s="10" t="n">
-        <v>4</v>
+      <c r="X41" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB41" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB41" s="4" t="n"/>
+      <c r="AC41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4964,11 +4958,11 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>7147084</v>
+        <v>7803937</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Chinese Tourism Advanced Toastmasters</t>
+          <t>Changeway Bilingual Suzhou Toastmasters Club</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -4986,13 +4980,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -5013,7 +5007,7 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -5024,14 +5018,14 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5042,14 +5036,14 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="10" t="n">
-        <v>1</v>
+      <c r="Z42" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
@@ -5069,15 +5063,15 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>6588791</v>
+        <v>7147084</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Dance &amp; Drama Toastmasters Club</t>
+          <t>Chinese Tourism Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5091,13 +5085,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -5105,11 +5099,11 @@
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O43" s="8" t="inlineStr">
@@ -5118,7 +5112,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>0</v>
@@ -5136,27 +5130,31 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X43" s="9" t="n">
-        <v>0</v>
+      <c r="X43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5170,15 +5168,15 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>28675841</v>
+        <v>6588791</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Lead Talk Toastmasters Club</t>
+          <t>Dance &amp; Drama Toastmasters Club</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5192,25 +5190,25 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr">
@@ -5219,10 +5217,10 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" s="9" t="n">
         <v>0</v>
@@ -5236,32 +5234,28 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W44" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X44" s="10" t="n">
-        <v>4</v>
+      <c r="V44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="10" t="n">
-        <v>1</v>
+      <c r="Z44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5275,15 +5269,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>28678691</v>
+        <v>28675841</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Suzhou Bay Toastmasters Club</t>
+          <t>Lead Talk Toastmasters Club</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5297,13 +5291,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5324,10 +5318,10 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
@@ -5341,11 +5335,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>0</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>4</v>
@@ -5353,16 +5347,20 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5376,15 +5374,15 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1122845</v>
+        <v>28678691</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Suzhou Toastmasters Club</t>
+          <t>Suzhou Bay Toastmasters Club</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5398,17 +5396,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5425,7 +5423,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5434,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" s="9" t="n">
         <v>0</v>
@@ -5443,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5454,20 +5452,16 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="10" t="n">
-        <v>1</v>
+      <c r="Z46" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC46" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5477,19 +5471,19 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>7391143</v>
+        <v>1122845</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>AACTP Suzhou Toastmasters</t>
+          <t>Suzhou Toastmasters Club</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5503,13 +5497,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5530,7 +5524,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5539,19 +5533,19 @@
         <v>0</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T47" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="10" t="n">
-        <v>4</v>
+      <c r="V47" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>4</v>
@@ -5566,11 +5560,11 @@
         <v>1</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC47" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -5586,15 +5580,15 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>6664026</v>
+        <v>7391143</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>C_Life E 1 Advanced Toastmasters Club</t>
+          <t>AACTP Suzhou Toastmasters</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5611,10 +5605,10 @@
         <v>13</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5652,11 +5646,11 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>0</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>4</v>
@@ -5664,16 +5658,20 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5687,15 +5685,15 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>7458832</v>
+        <v>6664026</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Suzhou RISE Toastmasters Club</t>
+          <t>C_Life E 1 Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5709,17 +5707,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5736,7 +5734,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -5745,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="10" t="n">
         <v>1</v>
@@ -5753,11 +5751,11 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="10" t="n">
-        <v>4</v>
+      <c r="V49" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W49" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>4</v>
@@ -5765,20 +5763,16 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="10" t="n">
-        <v>1</v>
+      <c r="Z49" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC49" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AC49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5792,11 +5786,11 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>7980859</v>
+        <v>28681050</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Wujiang Toastmasters Club</t>
+          <t>Suzhou Entrepreneurs TMC</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -5814,17 +5808,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5850,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -5859,13 +5853,13 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X50" s="10" t="n">
-        <v>4</v>
+      <c r="X50" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5876,14 +5870,8 @@
       <c r="AA50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC50" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB50" s="4" t="n"/>
+      <c r="AC50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5893,19 +5881,19 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>5991914</v>
+        <v>7458832</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Caohu Toastmasters Club</t>
+          <t>Suzhou RISE Toastmasters Club</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5919,17 +5907,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
@@ -5946,7 +5934,7 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="9" t="n">
         <v>0</v>
@@ -5955,36 +5943,40 @@
         <v>0</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>0</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -5994,15 +5986,15 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>28677181</v>
+        <v>7980859</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Diamond Wisdom Toastmasters Club</t>
+          <t>Wujiang Toastmasters Club</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -6023,14 +6015,14 @@
         <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="7" t="n">
@@ -6047,7 +6039,7 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="9" t="n">
         <v>0</v>
@@ -6056,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="9" t="n">
         <v>0</v>
@@ -6068,24 +6060,28 @@
         <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB52" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6099,15 +6095,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2732401</v>
+        <v>5991914</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>First Bilingual Wuxi Toastmasters Club</t>
+          <t>Caohu Toastmasters Club</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6121,17 +6117,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
@@ -6171,26 +6167,22 @@
       <c r="W53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X53" s="10" t="n">
-        <v>4</v>
+      <c r="X53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="10" t="n">
-        <v>1</v>
+      <c r="Z53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6204,11 +6196,11 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1995564</v>
+        <v>28677181</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Wuxi Advanced Toastmasters Club</t>
+          <t>Diamond Wisdom Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
@@ -6226,17 +6218,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="7" t="n">
@@ -6253,10 +6245,10 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -6264,38 +6256,34 @@
       <c r="S54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="10" t="n">
-        <v>1</v>
+      <c r="T54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>3</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Y54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB54" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC54" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6305,15 +6293,15 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>7959366</v>
+        <v>2732401</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Changeway Bilingual Wuxi</t>
+          <t>First Bilingual Wuxi Toastmasters Club</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -6331,17 +6319,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J55" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="J55" s="4" t="n">
-        <v>21</v>
-      </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="7" t="n">
@@ -6376,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6394,11 +6382,11 @@
         <v>1</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC55" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -6410,19 +6398,19 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>7769809</v>
+        <v>1995564</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Legend Toastmaster Club</t>
+          <t>Wuxi Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6436,17 +6424,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6466,42 +6454,46 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>0</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X56" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6515,15 +6507,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>744761</v>
+        <v>7959366</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>TaiHu Club</t>
+          <t>Changeway Bilingual Wuxi</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6537,25 +6529,25 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O57" s="8" t="inlineStr">
@@ -6582,13 +6574,13 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>0</v>
+      <c r="X57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6596,15 +6588,15 @@
       <c r="Z57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA57" s="9" t="n">
-        <v>0</v>
+      <c r="AA57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC57" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6620,15 +6612,15 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1174677</v>
+        <v>7769809</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Wuxi No. 1 Toastmasters Club</t>
+          <t>Legend Toastmaster Club</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6642,17 +6634,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="7" t="n">
@@ -6686,11 +6678,11 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="10" t="n">
-        <v>4</v>
+      <c r="V58" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>4</v>
@@ -6698,42 +6690,38 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="10" t="n">
-        <v>1</v>
+      <c r="Z58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>3820010</v>
+        <v>744761</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>DNA Bilingual Toastmasters</t>
+          <t>TaiHu Club</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6747,25 +6735,25 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr">
@@ -6792,13 +6780,13 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="10" t="n">
-        <v>7</v>
+      <c r="X59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6806,35 +6794,39 @@
       <c r="Z59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA59" s="10" t="n">
-        <v>1</v>
+      <c r="AA59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>3646256</v>
+        <v>1174677</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Nanjing First Mandarin Toastmasters Club</t>
+          <t>Wuxi No. 1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6848,13 +6840,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6884,13 +6876,13 @@
         <v>0</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T60" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V60" s="10" t="n">
         <v>4</v>
@@ -6911,11 +6903,11 @@
         <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -6931,11 +6923,11 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2164490</v>
+        <v>3820010</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Nanjing HROP Toastmasters Club</t>
+          <t>DNA Bilingual Toastmasters</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -6953,10 +6945,10 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1</v>
@@ -6989,40 +6981,36 @@
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T61" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T61" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X61" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC61" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7036,15 +7024,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1426404</v>
+        <v>3646256</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Nanjing No.1 Toastmasters Club</t>
+          <t>Nanjing First Mandarin Toastmasters Club</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7058,17 +7046,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -7085,7 +7073,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7094,36 +7082,40 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W62" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7133,15 +7125,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>7771807</v>
+        <v>2164490</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>AACTP Nanjing Toastmasters</t>
+          <t>Nanjing HROP Toastmasters Club</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -7159,17 +7151,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
@@ -7186,7 +7178,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7195,10 +7187,10 @@
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
@@ -7210,23 +7202,23 @@
         <v>0</v>
       </c>
       <c r="X63" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="AC63" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -7238,15 +7230,15 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>28675818</v>
+        <v>1426404</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Phoenix Contact China Toastmasters Club</t>
+          <t>Nanjing No.1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -7264,13 +7256,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7291,7 +7283,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7300,40 +7292,36 @@
         <v>0</v>
       </c>
       <c r="S64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="10" t="n">
-        <v>4</v>
+      <c r="X64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="10" t="n">
-        <v>1</v>
+      <c r="Z64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7347,15 +7335,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>7873669</v>
+        <v>7771807</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Zhenjiang No.1 Toastmasters Club</t>
+          <t>AACTP Nanjing Toastmasters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7369,13 +7357,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7396,7 +7384,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7405,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -7414,27 +7402,31 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7448,15 +7440,15 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>5530286</v>
+        <v>28675818</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>ZTE NJ Pegasus Toastmasters</t>
+          <t>Phoenix Contact China Toastmasters Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7470,13 +7462,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7506,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -7515,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7526,16 +7518,20 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -7545,19 +7541,19 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>7993754</v>
+        <v>7873669</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Changeway Bilingual Nanjing</t>
+          <t>Zhenjiang No.1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7571,17 +7567,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7607,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="9" t="n">
         <v>0</v>
@@ -7627,20 +7623,16 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="10" t="n">
-        <v>1</v>
+      <c r="Z67" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC67" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7650,19 +7642,19 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>28680607</v>
+        <v>5530286</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Huai Zhu Zhengyan Toastmasters Club</t>
+          <t>ZTE NJ Pegasus Toastmasters</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7676,17 +7668,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="7" t="n">
@@ -7721,25 +7713,25 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="9" t="n">
-        <v>2</v>
+      <c r="X68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="10" t="n">
-        <v>1</v>
+      <c r="Z68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC68" s="4" t="inlineStr"/>
     </row>
@@ -7755,11 +7747,11 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>7074227</v>
+        <v>7993754</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Nanjing Ferryman Toastmaster Club</t>
+          <t>Changeway Bilingual Nanjing</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -7777,13 +7769,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7860,11 +7852,11 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>28675713</v>
+        <v>28680607</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Nanjing Tietoevry Toastmasters Club</t>
+          <t>Huai Zhu Zhengyan Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -7882,17 +7874,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
@@ -7909,16 +7901,16 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70" s="9" t="n">
         <v>0</v>
@@ -7927,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7945,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC70" s="4" t="inlineStr"/>
     </row>
@@ -7961,11 +7953,11 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28678333</v>
+        <v>7074227</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Nanjing You Yan Toastmasters Club</t>
+          <t>Nanjing Ferryman Toastmaster Club</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -7983,17 +7975,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="7" t="n">
@@ -8028,13 +8020,13 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8046,11 +8038,11 @@
         <v>1</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC71" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -8062,19 +8054,19 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>7779631</v>
+        <v>28675713</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Autoliv GTG Toastmasters Club</t>
+          <t>Nanjing Tietoevry Toastmasters Club</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8088,17 +8080,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="7" t="n">
@@ -8115,16 +8107,16 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q72" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -8151,7 +8143,7 @@
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC72" s="4" t="inlineStr"/>
     </row>
@@ -8163,19 +8155,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>5453419</v>
+        <v>28678333</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Changzhou Bilingual Toastmasters Club</t>
+          <t>Nanjing You Yan Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8189,17 +8181,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="7" t="n">
@@ -8216,10 +8208,10 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -8233,14 +8225,14 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="10" t="n">
-        <v>4</v>
+      <c r="V73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
@@ -8272,15 +8264,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>28679300</v>
+        <v>7779631</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Changzhou Changeway Bilingual Toastmasters Club</t>
+          <t>Autoliv GTG Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8294,13 +8286,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8321,11 +8313,11 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
       </c>
@@ -8339,13 +8331,13 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="10" t="n">
-        <v>7</v>
+      <c r="X74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8357,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC74" s="4" t="inlineStr"/>
     </row>
@@ -8373,15 +8365,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>5316020</v>
+        <v>5453419</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Changzhou No.1 Toastmasters Club</t>
+          <t>Changzhou Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8395,17 +8387,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="7" t="n">
@@ -8422,7 +8414,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>1</v>
@@ -8439,12 +8431,12 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
+      <c r="V75" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W75" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W75" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X75" s="10" t="n">
         <v>4</v>
       </c>
@@ -8460,7 +8452,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8474,15 +8470,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>7209054</v>
+        <v>28679300</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Changzhou Smart Toastmasters Club</t>
+          <t>Changzhou Changeway Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8496,17 +8492,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="7" t="n">
@@ -8523,7 +8519,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>0</v>
@@ -8540,14 +8536,14 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="10" t="n">
-        <v>4</v>
+      <c r="V76" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8559,35 +8555,31 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>6100252</v>
+        <v>5316020</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>A.A.C.T.P Wuhan</t>
+          <t>Changzhou No.1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8601,17 +8593,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
@@ -8630,17 +8622,17 @@
       <c r="P77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" s="10" t="n">
-        <v>2</v>
+      <c r="Q77" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8666,29 +8658,25 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>28676869</v>
+        <v>7209054</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Changeway Wu Han Toastmasters Club</t>
+          <t>Changzhou Smart Toastmasters Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -8706,13 +8694,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J78" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="K78" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8736,13 +8724,13 @@
         <v>1</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -8754,10 +8742,10 @@
         <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8769,11 +8757,11 @@
         <v>1</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -8789,11 +8777,11 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2793285</v>
+        <v>6100252</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Optics Valley Toastmasters Club</t>
+          <t>A.A.C.T.P Wuhan</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -8811,13 +8799,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8837,8 +8825,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P79" s="10" t="n">
-        <v>5</v>
+      <c r="P79" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q79" s="10" t="n">
         <v>2</v>
@@ -8847,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U79" s="9" t="n">
         <v>0</v>
@@ -8859,7 +8847,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>4</v>
@@ -8874,11 +8862,11 @@
         <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC79" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -8894,15 +8882,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>28676663</v>
+        <v>28676869</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Wuhan Century Excellence</t>
+          <t>Changeway Wu Han Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8916,13 +8904,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8943,10 +8931,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8960,20 +8948,20 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>0</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="X80" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8995,19 +8983,19 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>7837341</v>
+        <v>2793285</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>AACTP Jingchu Trainer Club</t>
+          <t>Optics Valley Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9021,17 +9009,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M81" s="7" t="n">
@@ -9047,11 +9035,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="9" t="n">
-        <v>0</v>
+      <c r="P81" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -9065,12 +9053,12 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
+      <c r="V81" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W81" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W81" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X81" s="10" t="n">
         <v>4</v>
       </c>
@@ -9084,9 +9072,13 @@
         <v>1</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9096,19 +9088,19 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>5409847</v>
+        <v>28676663</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>HanyangPIE</t>
+          <t>Wuhan Century Excellence</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9122,17 +9114,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="7" t="n">
@@ -9167,7 +9159,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9178,8 +9170,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="10" t="n">
-        <v>1</v>
+      <c r="Z82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9205,11 +9197,11 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1273965</v>
+        <v>7837341</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Wuhan No.1 Toastmasters Club</t>
+          <t>AACTP Jingchu Trainer Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -9227,17 +9219,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="7" t="n">
@@ -9254,7 +9246,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9278,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -9292,11 +9284,7 @@
       <c r="AB83" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9310,11 +9298,11 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>28676821</v>
+        <v>5409847</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>YCI Toastmasters Club</t>
+          <t>HanyangPIE</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -9332,13 +9320,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -9383,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="X84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9395,9 +9383,13 @@
         <v>1</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9407,15 +9399,15 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>28675403</v>
+        <v>1273965</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>AACTP ChangSha Mascot TMC</t>
+          <t>Wuhan No.1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -9433,17 +9425,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="7" t="n">
@@ -9460,7 +9452,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -9484,19 +9476,19 @@
         <v>0</v>
       </c>
       <c r="X85" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB85" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="Y85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA85" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB85" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="AC85" s="4" t="inlineStr">
         <is>
@@ -9512,15 +9504,15 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7322642</v>
+        <v>28676821</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Changsha Another TMC</t>
+          <t>YCI Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -9538,17 +9530,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="7" t="n">
@@ -9565,7 +9557,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9583,13 +9575,13 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="10" t="n">
-        <v>5</v>
+      <c r="X86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9601,13 +9593,9 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC86" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9621,15 +9609,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1363453</v>
+        <v>28675403</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Changsha No. 1 Toastmasters Club</t>
+          <t>AACTP ChangSha Mascot TMC</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9643,17 +9631,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="7" t="n">
@@ -9670,31 +9658,31 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S87" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T87" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U87" s="10" t="n">
-        <v>1</v>
+      <c r="S87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V87" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9706,11 +9694,11 @@
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC87" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -9726,11 +9714,11 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>7622962</v>
+        <v>7322642</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Unlock Online English Toastmasters Club</t>
+          <t>Changsha Another TMC</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -9748,17 +9736,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="7" t="n">
@@ -9775,7 +9763,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9811,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -9827,19 +9815,19 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>6659579</v>
+        <v>1363453</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>AACTP CS TMC</t>
+          <t>Changsha No. 1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9853,17 +9841,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="7" t="n">
@@ -9883,7 +9871,7 @@
         <v>3</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9891,20 +9879,20 @@
       <c r="S89" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="9" t="n">
-        <v>0</v>
+      <c r="T89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9932,19 +9920,19 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>28675369</v>
+        <v>7622962</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Changsha Lujianghui Toastmasters Club</t>
+          <t>Unlock Online English Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9958,17 +9946,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="7" t="n">
@@ -9985,10 +9973,10 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9996,20 +9984,20 @@
       <c r="S90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T90" s="10" t="n">
-        <v>1</v>
+      <c r="T90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>2</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -10021,11 +10009,11 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10041,11 +10029,11 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>28675405</v>
+        <v>6659579</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>CS South Toastmaster Club</t>
+          <t>AACTP CS TMC</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -10063,17 +10051,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="7" t="n">
@@ -10090,16 +10078,16 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="9" t="n">
-        <v>0</v>
+      <c r="S91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10107,14 +10095,14 @@
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="10" t="n">
-        <v>4</v>
+      <c r="V91" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10126,9 +10114,13 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10142,15 +10134,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>2484056</v>
+        <v>28675369</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>FedEx Toastmasters Club @ Wuhan</t>
+          <t>Changsha Lujianghui Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10164,13 +10156,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
@@ -10191,7 +10183,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -10202,20 +10194,20 @@
       <c r="S92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>0</v>
+      <c r="X92" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -10227,9 +10219,13 @@
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC92" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC92" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10243,15 +10239,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>7854906</v>
+        <v>28675405</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Nanchang Toastmasters Club</t>
+          <t>CS South Toastmaster Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10265,13 +10261,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -10292,10 +10288,10 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -10309,11 +10305,11 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>1</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>4</v>
@@ -10328,27 +10324,27 @@
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>28679246</v>
+        <v>2484056</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Ningbo A Tree Toastmasters Club</t>
+          <t>FedEx Toastmasters Club @ Wuhan</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -10366,17 +10362,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="7" t="n">
@@ -10411,13 +10407,13 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="10" t="n">
-        <v>7</v>
+      <c r="X94" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10429,31 +10425,27 @@
         <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>5371854</v>
+        <v>7854906</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Ningbo Better Man Toastmasters Club</t>
+          <t>Nanchang Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -10471,10 +10463,10 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K95" s="4" t="n">
         <v>1</v>
@@ -10498,7 +10490,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10521,8 +10513,8 @@
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="9" t="n">
-        <v>1</v>
+      <c r="X95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -10534,7 +10526,7 @@
         <v>1</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC95" s="4" t="inlineStr"/>
     </row>
@@ -10550,15 +10542,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2478206</v>
+        <v>28679246</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Ningbo No. 1 Toastmasters Club</t>
+          <t>Ningbo A Tree Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10572,17 +10564,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10599,28 +10591,28 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="10" t="n">
-        <v>4</v>
+      <c r="V96" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>7</v>
@@ -10655,11 +10647,11 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>5346829</v>
+        <v>5371854</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Ningbo XMA Toastmasters Club</t>
+          <t>Ningbo Better Man Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -10677,13 +10669,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10722,13 +10714,13 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="10" t="n">
-        <v>4</v>
+      <c r="X97" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10740,7 +10732,7 @@
         <v>1</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC97" s="4" t="inlineStr"/>
     </row>
@@ -10756,15 +10748,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>5742730</v>
+        <v>2478206</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Star T.T.T. Toastmasters Club</t>
+          <t>Ningbo No. 1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10778,13 +10770,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10808,19 +10800,19 @@
         <v>3</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="10" t="n">
-        <v>3</v>
+      <c r="S98" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T98" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U98" s="10" t="n">
-        <v>1</v>
+      <c r="U98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V98" s="10" t="n">
         <v>4</v>
@@ -10845,7 +10837,7 @@
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -10857,19 +10849,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>7302685</v>
+        <v>5346829</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Jinhua NO.1  Toastmasters Club</t>
+          <t>Ningbo XMA Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10883,17 +10875,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="7" t="n">
@@ -10910,10 +10902,10 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10927,32 +10919,28 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="10" t="n">
-        <v>4</v>
+      <c r="V99" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z99" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA99" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB99" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC99" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10962,19 +10950,19 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>5380138</v>
+        <v>5742730</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Yi Wu No. 1 Toastmasters Club</t>
+          <t>Star T.T.T. Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10988,13 +10976,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11014,8 +11002,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>0</v>
+      <c r="P100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -11023,20 +11011,20 @@
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
+      <c r="S100" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W100" s="10" t="n">
-        <v>4</v>
+      <c r="W100" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>7</v>
@@ -11055,7 +11043,7 @@
       </c>
       <c r="AC100" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -11071,15 +11059,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28679552</v>
+        <v>7302685</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Yiwu Distinguished Parents Toastmasters Club</t>
+          <t>Jinhua NO.1  Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11093,17 +11081,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -11119,8 +11107,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P101" s="10" t="n">
-        <v>5</v>
+      <c r="P101" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>1</v>
@@ -11128,23 +11116,23 @@
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S101" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T101" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" s="9" t="n">
-        <v>1</v>
+      <c r="S101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X101" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11176,15 +11164,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>7983964</v>
+        <v>5380138</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Yiwu Fortune Toastmasters Club</t>
+          <t>Yi Wu No. 1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11198,13 +11186,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11234,7 +11222,7 @@
         <v>0</v>
       </c>
       <c r="S102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" s="9" t="n">
         <v>0</v>
@@ -11245,11 +11233,11 @@
       <c r="V102" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W102" s="9" t="n">
-        <v>2</v>
+      <c r="W102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11281,15 +11269,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28678344</v>
+        <v>28679552</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Yiwu Leaders' Toastmasters Club</t>
+          <t>Yiwu Distinguished Parents Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11303,17 +11291,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -11330,13 +11318,13 @@
         </is>
       </c>
       <c r="P103" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q103" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R103" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="Q103" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S103" s="10" t="n">
         <v>2</v>
@@ -11344,17 +11332,17 @@
       <c r="T103" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" s="10" t="n">
-        <v>4</v>
+      <c r="U103" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X103" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11382,19 +11370,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>5989825</v>
+        <v>7983964</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Ningbo Tianyi Youth Toastmasters Club</t>
+          <t>Yiwu Fortune Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11408,17 +11396,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="7" t="n">
@@ -11444,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="9" t="n">
         <v>0</v>
@@ -11452,14 +11440,14 @@
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
+      <c r="V104" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W104" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W104" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X104" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11475,7 +11463,7 @@
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11487,19 +11475,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28680187</v>
+        <v>28678344</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Ninghai TaoYuanLi Toastmasters Club</t>
+          <t>Yiwu Leaders' Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11513,13 +11501,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11539,29 +11527,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P105" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="P105" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q105" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R105" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S105" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>0</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11576,9 +11564,13 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11592,11 +11584,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>4646640</v>
+        <v>5989825</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Taizhou No.1 Toastmasters Club</t>
+          <t>Ningbo Tianyi Youth Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -11614,13 +11606,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11659,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11677,9 +11669,13 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11693,11 +11689,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>5200740</v>
+        <v>28680187</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Taizhou OUR Toastmasters Club</t>
+          <t>Ninghai TaoYuanLi Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11715,13 +11711,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11742,7 +11738,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11760,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11778,13 +11774,9 @@
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11798,11 +11790,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7700569</v>
+        <v>4646640</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Wenling Beacon Toastmasters Club</t>
+          <t>Taizhou No.1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11823,10 +11815,10 @@
         <v>9</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11865,13 +11857,13 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11883,7 +11875,7 @@
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC108" s="4" t="inlineStr"/>
     </row>
@@ -11895,19 +11887,19 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>5789778</v>
+        <v>5200740</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Fenghua No. 1 Toastmasters Club</t>
+          <t>Taizhou OUR Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11921,17 +11913,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="7" t="n">
@@ -11947,8 +11939,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P109" s="9" t="n">
-        <v>0</v>
+      <c r="P109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11972,7 +11964,7 @@
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -12000,19 +11992,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>7317700</v>
+        <v>7700569</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Keqiao Bilingual Speech Club</t>
+          <t>Wenling Beacon Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12026,13 +12018,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -12064,8 +12056,8 @@
       <c r="S110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
@@ -12077,7 +12069,7 @@
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12105,15 +12097,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28678544</v>
+        <v>5789778</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Shangyu Qingchun Mengxiang Toastmasters Club</t>
+          <t>Fenghua No. 1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12127,13 +12119,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12153,11 +12145,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P111" s="10" t="n">
-        <v>6</v>
+      <c r="P111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12172,13 +12164,13 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12190,11 +12182,11 @@
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC111" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12210,11 +12202,11 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6764681</v>
+        <v>7317700</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Shaoxing No. 1 Toastmasters Club</t>
+          <t>Keqiao Bilingual Speech Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -12232,13 +12224,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -12262,7 +12254,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12283,7 +12275,7 @@
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12295,27 +12287,27 @@
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>4757747</v>
+        <v>28678544</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>A.A.C.T.P HZ Toastmasters</t>
+          <t>Shangyu Qingchun Mengxiang Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -12333,17 +12325,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="7" t="n">
@@ -12359,11 +12351,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P113" s="9" t="n">
-        <v>1</v>
+      <c r="P113" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12377,14 +12369,14 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="10" t="n">
-        <v>4</v>
+      <c r="V113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12396,31 +12388,35 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28676667</v>
+        <v>6764681</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Changeway Bilingual Hangzhou</t>
+          <t>Shaoxing No. 1 Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12434,13 +12430,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -12461,10 +12457,10 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12472,14 +12468,14 @@
       <c r="S114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12497,7 +12493,7 @@
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC114" s="4" t="inlineStr"/>
     </row>
@@ -12513,15 +12509,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>7548547</v>
+        <v>4757747</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Jiaxing Think &amp; Talk Bilingual Toastmasters Club</t>
+          <t>A.A.C.T.P HZ Toastmasters</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12535,10 +12531,10 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>0</v>
@@ -12562,7 +12558,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12579,26 +12575,26 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>0</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AC115" s="4" t="inlineStr"/>
     </row>
@@ -12614,15 +12610,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>6594839</v>
+        <v>28676667</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Top Bilingual Toastmasters Club</t>
+          <t>Changeway Bilingual Hangzhou</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12636,13 +12632,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12663,7 +12659,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -12680,26 +12676,26 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>2</v>
+      <c r="X116" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC116" s="4" t="inlineStr"/>
     </row>
@@ -12715,15 +12711,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1224488</v>
+        <v>7548547</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>WestLake Bilingual</t>
+          <t>Jiaxing Think &amp; Talk Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12737,17 +12733,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="7" t="n">
@@ -12764,49 +12760,45 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC117" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12816,19 +12808,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>6854355</v>
+        <v>6594839</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>DREAMTOWN BILINGUAL TOASTMASTERS CLUB</t>
+          <t>Top Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12842,13 +12834,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12869,7 +12861,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
@@ -12887,25 +12879,25 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="10" t="n">
-        <v>5</v>
+      <c r="X118" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="10" t="n">
-        <v>1</v>
+      <c r="Z118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC118" s="4" t="inlineStr"/>
     </row>
@@ -12917,19 +12909,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>7854443</v>
+        <v>1224488</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Future Champion Advanced Toastmasters Club</t>
+          <t>WestLake Bilingual</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12943,17 +12935,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
@@ -12970,25 +12962,25 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q119" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q119" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="10" t="n">
-        <v>3</v>
+      <c r="S119" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
+      <c r="U119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -13006,11 +12998,11 @@
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC119" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -13026,15 +13018,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>5677273</v>
+        <v>6854355</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Lakeside Bilingual Toastmasters Club</t>
+          <t>DREAMTOWN BILINGUAL TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13048,17 +13040,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -13075,7 +13067,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -13092,14 +13084,14 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>2</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13111,13 +13103,9 @@
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13131,15 +13119,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28680643</v>
+        <v>7854443</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>She Speaks Toastmasters Club</t>
+          <t>Future Champion Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13153,13 +13141,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13180,19 +13168,19 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="S121" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
@@ -13204,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13216,9 +13204,13 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC121" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13232,15 +13224,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>6894445</v>
+        <v>5677273</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Zhejiang University Toastmasters Club</t>
+          <t>Lakeside Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13254,13 +13246,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -13281,7 +13273,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -13304,22 +13296,26 @@
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>0</v>
+      <c r="X122" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13329,39 +13325,39 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>5000401</v>
+        <v>28680643</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Hangzhou M.A.D. Toastmasters Club</t>
+          <t>She Speaks Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K123" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F123" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G123" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J123" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="K123" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13385,28 +13381,28 @@
         <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -13418,13 +13414,9 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC123" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13434,19 +13426,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1199621</v>
+        <v>6894445</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Hangzhou METALK Toastmasters Club</t>
+          <t>Zhejiang University Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13460,17 +13452,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -13487,7 +13479,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -13496,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" s="9" t="n">
         <v>0</v>
@@ -13504,32 +13496,28 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="10" t="n">
-        <v>4</v>
+      <c r="V124" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X124" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="10" t="n">
-        <v>1</v>
+      <c r="Z124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC124" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13543,15 +13531,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1803802</v>
+        <v>5000401</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Qiantang Bilingual Toastmasters Club</t>
+          <t>Hangzhou M.A.D. Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13565,25 +13553,25 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-14</v>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O125" s="8" t="inlineStr">
@@ -13592,31 +13580,31 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X125" s="9" t="n">
-        <v>0</v>
+      <c r="X125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13624,13 +13612,17 @@
       <c r="Z125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA125" s="9" t="n">
-        <v>0</v>
+      <c r="AA125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13644,15 +13636,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>6591407</v>
+        <v>1199621</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>XIASHA Toastmasters Club</t>
+          <t>Hangzhou METALK Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13666,17 +13658,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -13693,7 +13685,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
@@ -13704,8 +13696,8 @@
       <c r="S126" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T126" s="10" t="n">
-        <v>1</v>
+      <c r="T126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
@@ -13714,10 +13706,10 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13729,9 +13721,13 @@
         <v>1</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13741,19 +13737,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>7950547</v>
+        <v>1803802</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Hangzhou R.I.S.E. Toastmasters Club</t>
+          <t>Qiantang Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13767,13 +13763,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J127" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J127" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L127" s="8" t="inlineStr">
         <is>
@@ -13781,11 +13777,11 @@
         </is>
       </c>
       <c r="M127" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O127" s="8" t="inlineStr">
@@ -13812,13 +13808,13 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="10" t="n">
-        <v>5</v>
+      <c r="X127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13826,11 +13822,11 @@
       <c r="Z127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA127" s="10" t="n">
-        <v>1</v>
+      <c r="AA127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC127" s="4" t="inlineStr"/>
     </row>
@@ -13842,19 +13838,19 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1376206</v>
+        <v>6591407</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>State Street Hangzhou Toastmasters Club</t>
+          <t>XIASHA Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13868,17 +13864,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L128" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13904,22 +13900,22 @@
         <v>0</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>2</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="X128" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13931,7 +13927,7 @@
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC128" s="4" t="inlineStr"/>
     </row>
@@ -13947,15 +13943,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>7699070</v>
+        <v>7950547</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Xiaoshan BTS Toastmasters Club</t>
+          <t>Hangzhou R.I.S.E. Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13969,17 +13965,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="7" t="n">
@@ -13998,29 +13994,29 @@
       <c r="P129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" s="10" t="n">
-        <v>2</v>
+      <c r="Q129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T129" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U129" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -14032,13 +14028,9 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC129" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14052,15 +14044,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>7626845</v>
+        <v>1376206</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Xiaoshan No. 1 Mandarin Toastmasters</t>
+          <t>State Street Hangzhou Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14074,17 +14066,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -14101,52 +14093,258 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" s="9" t="n">
+      <c r="W130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>7699070</v>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Xiaoshan BTS Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J131" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K131" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M131" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O131" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>7626845</v>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Xiaoshan No. 1 Mandarin Toastmasters</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="W130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" s="10" t="n">
+      <c r="F132" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J132" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K132" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M132" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O132" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P132" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB130" s="4" t="n">
+      <c r="Y132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr">
+      <c r="AC132" s="4" t="inlineStr">
         <is>
           <t>President's Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC130"/>
+  <autoFilter ref="A1:AC132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14233,7 +14431,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14248,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -14281,7 +14479,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -14314,7 +14512,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -14347,7 +14545,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14365,7 +14563,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -14413,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -14446,7 +14644,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -14479,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -14497,7 +14695,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14512,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -14527,7 +14725,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -14536,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -14560,7 +14758,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -14569,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -14596,7 +14794,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14611,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14644,7 +14842,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -14662,13 +14860,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -14710,7 +14908,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14743,7 +14941,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -14761,7 +14959,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14776,7 +14974,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -14809,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -14842,7 +15040,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -14860,7 +15058,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -14875,7 +15073,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14908,7 +15106,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -14926,7 +15124,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -14941,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -14974,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14992,7 +15190,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15007,7 +15205,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -15040,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -15058,7 +15256,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15073,7 +15271,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -15091,7 +15289,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -15106,7 +15304,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -15139,7 +15337,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -15172,7 +15370,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:07 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:07 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>2</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1831,8 +1831,8 @@
       <c r="U11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="9" t="n">
-        <v>3</v>
+      <c r="V11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>4</v>
@@ -3443,13 +3443,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>4</v>
       </c>
       <c r="W35" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>4</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>0</v>
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -5291,13 +5291,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -6529,13 +6529,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -7769,13 +7769,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>4</v>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9219,13 +9219,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -9263,8 +9263,8 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>2</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9461,10 +9461,10 @@
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9774,8 +9774,8 @@
       <c r="S88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10077,8 +10077,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P91" s="9" t="n">
-        <v>3</v>
+      <c r="P91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10156,13 +10156,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
@@ -10770,13 +10770,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>7</v>
@@ -11913,13 +11913,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -12531,13 +12531,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>6</v>
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13351,13 +13351,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13395,11 +13395,11 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>3</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>5</v>
@@ -14497,7 +14497,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15025,7 +15025,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15058,7 +15058,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -15091,7 +15091,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/128/inyear.xlsx
+++ b/docs/d/128/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2951,8 +2951,8 @@
       <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="9" t="n">
-        <v>1</v>
+      <c r="Q22" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4614,8 +4614,8 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>2</v>
+      <c r="V38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
         <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -5129,11 +5129,11 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>3</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>4</v>
@@ -5291,13 +5291,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -7046,13 +7046,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>4</v>
@@ -7256,13 +7256,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7695,16 +7695,16 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -10051,13 +10051,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -12045,10 +12045,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12531,13 +12531,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12578,8 +12578,8 @@
       <c r="V115" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W115" s="9" t="n">
-        <v>3</v>
+      <c r="W115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>6</v>
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>5</v>
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14272,13 +14272,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
@@ -14316,11 +14316,11 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>3</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>5</v>
@@ -14596,7 +14596,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14728,7 +14728,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15256,7 +15256,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15355,7 +15355,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
